--- a/src/main/resources/doc/PONKIDS-테이블목록_v1.5.xlsx
+++ b/src/main/resources/doc/PONKIDS-테이블목록_v1.5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01.피오니키즈\02.분석\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonna\git\pioneerkidsDev\src\main\resources\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EA801FF-3DF7-4495-B30C-F222553FDC7E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39DC7790-B6D3-4722-B7AB-D1A94F093B6D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,9 +19,9 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'테이블 목록'!$A$3:$F$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'테이블 목록'!$A$3:$F$33</definedName>
     <definedName name="baseline">'[1]2.일정추적'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'테이블 목록'!$A$1:$F$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'테이블 목록'!$A$1:$F$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'테이블 목록'!$1:$3</definedName>
     <definedName name="rpt_date">'[1]1.요약'!$C$4</definedName>
     <definedName name="T01_컬럼정보_Query">#REF!</definedName>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="105">
   <si>
     <t>테이블명</t>
     <phoneticPr fontId="11" type="noConversion"/>
@@ -390,14 +390,6 @@
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
   <si>
-    <t>TB_BBS_ROLE</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시판권한</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
     <t>설문조사</t>
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
@@ -434,10 +426,6 @@
   </si>
   <si>
     <t>설문조사질문상세</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시판 권한 관리 테이블</t>
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
   <si>
@@ -1556,7 +1544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.5546875" style="9" customWidth="1"/>
@@ -2292,11 +2280,11 @@
         <v>32</v>
       </c>
       <c r="G5" s="16" t="str">
-        <f t="shared" ref="G5:G34" si="0">"CREATE TABLE "&amp; D5 &amp; " ( ); "</f>
+        <f t="shared" ref="G5:G33" si="0">"CREATE TABLE "&amp; D5 &amp; " ( ); "</f>
         <v xml:space="preserve">CREATE TABLE TB_USER_CHLDRN ( ); </v>
       </c>
       <c r="H5" s="16" t="str">
-        <f t="shared" ref="H5:H36" si="1">"COMMENT ON TABLE "&amp;D5&amp;" IS '"&amp;F5&amp;"' ;"</f>
+        <f t="shared" ref="H5:H35" si="1">"COMMENT ON TABLE "&amp;D5&amp;" IS '"&amp;F5&amp;"' ;"</f>
         <v>COMMENT ON TABLE TB_USER_CHLDRN IS '사용자 자녀 관리 테이블' ;</v>
       </c>
     </row>
@@ -2666,7 +2654,7 @@
     </row>
     <row r="19" spans="1:8" s="16" customFormat="1">
       <c r="A19" s="27">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19" s="25" t="s">
         <v>7</v>
@@ -2675,26 +2663,26 @@
         <v>13</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="G19" s="16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">CREATE TABLE TB_BBS_ROLE ( ); </v>
+        <v xml:space="preserve">CREATE TABLE TB_NTT ( ); </v>
       </c>
       <c r="H19" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE TB_BBS_ROLE IS '게시판 권한 관리 테이블' ;</v>
+        <v>COMMENT ON TABLE TB_NTT IS '게시물 관리 테이블' ;</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="16" customFormat="1">
       <c r="A20" s="27">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" s="25" t="s">
         <v>7</v>
@@ -2703,194 +2691,194 @@
         <v>13</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="G20" s="16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">CREATE TABLE TB_NTT ( ); </v>
+        <v xml:space="preserve">CREATE TABLE TB_NTT_ANSWER ( ); </v>
       </c>
       <c r="H20" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE TB_NTT IS '게시물 관리 테이블' ;</v>
+        <v>COMMENT ON TABLE TB_NTT_ANSWER IS '게시판 댓글 내역 관리 테이블' ;</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="16" customFormat="1">
       <c r="A21" s="27">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" s="25" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>63</v>
+        <v>89</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>90</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="G21" s="16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">CREATE TABLE TB_NTT_ANSWER ( ); </v>
+        <v xml:space="preserve">CREATE TABLE TB_QESTNAR_GROUP ( ); </v>
       </c>
       <c r="H21" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE TB_NTT_ANSWER IS '게시판 댓글 내역 관리 테이블' ;</v>
+        <v>COMMENT ON TABLE TB_QESTNAR_GROUP IS '설문조사 그룹 관리 테이블' ;</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="16" customFormat="1">
       <c r="A22" s="27">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" s="25" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>92</v>
-      </c>
       <c r="E22" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G22" s="16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">CREATE TABLE TB_QESTNAR_GROUP ( ); </v>
+        <v xml:space="preserve">CREATE TABLE TB_QESTNAR_QESTN ( ); </v>
       </c>
       <c r="H22" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE TB_QESTNAR_GROUP IS '설문조사 그룹 관리 테이블' ;</v>
+        <v>COMMENT ON TABLE TB_QESTNAR_QESTN IS '설문조사 질문 관리 테이블' ;</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="16" customFormat="1">
       <c r="A23" s="27">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="25" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G23" s="16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">CREATE TABLE TB_QESTNAR_QESTN ( ); </v>
+        <v xml:space="preserve">CREATE TABLE TB_QESTNAR_QESTN_DETAIL ( ); </v>
       </c>
       <c r="H23" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE TB_QESTNAR_QESTN IS '설문조사 질문 관리 테이블' ;</v>
+        <v>COMMENT ON TABLE TB_QESTNAR_QESTN_DETAIL IS '설문조사 질문 상세 관리 테이블' ;</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="16" customFormat="1">
       <c r="A24" s="27">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" s="25" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G24" s="16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">CREATE TABLE TB_QESTNAR_QESTN_DETAIL ( ); </v>
+        <v xml:space="preserve">CREATE TABLE TB_QESTNAR_ANSWER ( ); </v>
       </c>
       <c r="H24" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE TB_QESTNAR_QESTN_DETAIL IS '설문조사 질문 상세 관리 테이블' ;</v>
+        <v>COMMENT ON TABLE TB_QESTNAR_ANSWER IS '설문조사 답변 관리 테이블' ;</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="16" customFormat="1">
       <c r="A25" s="27">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" s="25" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G25" s="16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">CREATE TABLE TB_QESTNAR_ANSWER ( ); </v>
+        <v xml:space="preserve">CREATE TABLE TB_QESTNAR_ANSWER_DETAIL ( ); </v>
       </c>
       <c r="H25" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE TB_QESTNAR_ANSWER IS '설문조사 답변 관리 테이블' ;</v>
+        <v>COMMENT ON TABLE TB_QESTNAR_ANSWER_DETAIL IS '설문조사 답변 상세 관리 테이블' ;</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="16" customFormat="1">
       <c r="A26" s="27">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26" s="25" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>96</v>
+        <v>15</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="G26" s="16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">CREATE TABLE TB_QESTNAR_ANSWER_DETAIL ( ); </v>
+        <v xml:space="preserve">CREATE TABLE TB_POPUP ( ); </v>
       </c>
       <c r="H26" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE TB_QESTNAR_ANSWER_DETAIL IS '설문조사 답변 상세 관리 테이블' ;</v>
+        <v>COMMENT ON TABLE TB_POPUP IS '팝업 관리 테이블' ;</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="16" customFormat="1">
       <c r="A27" s="27">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" s="25" t="s">
         <v>7</v>
@@ -2899,26 +2887,26 @@
         <v>15</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="G27" s="16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">CREATE TABLE TB_POPUP ( ); </v>
+        <v xml:space="preserve">CREATE TABLE TB_ATCH_FILE ( ); </v>
       </c>
       <c r="H27" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE TB_POPUP IS '팝업 관리 테이블' ;</v>
+        <v>COMMENT ON TABLE TB_ATCH_FILE IS '첨부 파일 관리 테이블' ;</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="16" customFormat="1">
       <c r="A28" s="27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28" s="25" t="s">
         <v>7</v>
@@ -2927,26 +2915,26 @@
         <v>15</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G28" s="16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">CREATE TABLE TB_ATCH_FILE ( ); </v>
+        <v xml:space="preserve">CREATE TABLE TB_ATCH_FILE_DETAIL ( ); </v>
       </c>
       <c r="H28" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE TB_ATCH_FILE IS '첨부 파일 관리 테이블' ;</v>
+        <v>COMMENT ON TABLE TB_ATCH_FILE_DETAIL IS '첨부 파일 상세 관리 테이블' ;</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="16" customFormat="1">
       <c r="A29" s="27">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29" s="25" t="s">
         <v>7</v>
@@ -2955,26 +2943,26 @@
         <v>15</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="G29" s="16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">CREATE TABLE TB_ATCH_FILE_DETAIL ( ); </v>
+        <v xml:space="preserve">CREATE TABLE TB_MENU ( ); </v>
       </c>
       <c r="H29" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE TB_ATCH_FILE_DETAIL IS '첨부 파일 상세 관리 테이블' ;</v>
+        <v>COMMENT ON TABLE TB_MENU IS '메뉴 관리 테이블' ;</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="16" customFormat="1">
       <c r="A30" s="27">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B30" s="25" t="s">
         <v>7</v>
@@ -2983,26 +2971,26 @@
         <v>15</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G30" s="16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">CREATE TABLE TB_MENU ( ); </v>
+        <v xml:space="preserve">CREATE TABLE TB_MENU_ROLE ( ); </v>
       </c>
       <c r="H30" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE TB_MENU IS '메뉴 관리 테이블' ;</v>
+        <v>COMMENT ON TABLE TB_MENU_ROLE IS '메뉴 권한 테이블' ;</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="16" customFormat="1">
       <c r="A31" s="27">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31" s="25" t="s">
         <v>7</v>
@@ -3011,26 +2999,26 @@
         <v>15</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G31" s="16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">CREATE TABLE TB_MENU_ROLE ( ); </v>
+        <v xml:space="preserve">CREATE TABLE TB_CMMN_CD ( ); </v>
       </c>
       <c r="H31" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE TB_MENU_ROLE IS '메뉴 권한 테이블' ;</v>
+        <v>COMMENT ON TABLE TB_CMMN_CD IS '공통 코드 관리 테이블' ;</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="16" customFormat="1">
       <c r="A32" s="27">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32" s="25" t="s">
         <v>7</v>
@@ -3039,26 +3027,26 @@
         <v>15</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G32" s="16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">CREATE TABLE TB_CMMN_CD ( ); </v>
+        <v xml:space="preserve">CREATE TABLE TB_CMMN_CD_DETAIL ( ); </v>
       </c>
       <c r="H32" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE TB_CMMN_CD IS '공통 코드 관리 테이블' ;</v>
+        <v>COMMENT ON TABLE TB_CMMN_CD_DETAIL IS '공통 코드 상세 관리 테이블' ;</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="16" customFormat="1">
       <c r="A33" s="27">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33" s="25" t="s">
         <v>7</v>
@@ -3067,26 +3055,26 @@
         <v>15</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G33" s="16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">CREATE TABLE TB_CMMN_CD_DETAIL ( ); </v>
+        <v xml:space="preserve">CREATE TABLE TB_BANNER ( ); </v>
       </c>
       <c r="H33" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE TB_CMMN_CD_DETAIL IS '공통 코드 상세 관리 테이블' ;</v>
+        <v>COMMENT ON TABLE TB_BANNER IS '배너 관리 테이블' ;</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="16" customFormat="1">
       <c r="A34" s="27">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34" s="25" t="s">
         <v>7</v>
@@ -3094,27 +3082,23 @@
       <c r="C34" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="D34" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="G34" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">CREATE TABLE TB_BANNER ( ); </v>
+      <c r="D34" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>78</v>
       </c>
       <c r="H34" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE TB_BANNER IS '배너 관리 테이블' ;</v>
+        <v>COMMENT ON TABLE  + 로그성 테이블 추가 예정 +  IS ' + 로그성 테이블 추가 예정 + ' ;</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="16" customFormat="1">
       <c r="A35" s="27">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35" s="25" t="s">
         <v>7</v>
@@ -3123,42 +3107,24 @@
         <v>15</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H35" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE  + 로그성 테이블 추가 예정 +  IS ' + 로그성 테이블 추가 예정 + ' ;</v>
+        <v>COMMENT ON TABLE  + 통계성 테이블 추가 예정 +  IS ' + 통계성 테이블 추가 예정 + ' ;</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="16" customFormat="1">
-      <c r="A36" s="27">
-        <v>33</v>
-      </c>
-      <c r="B36" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="F36" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="H36" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>COMMENT ON TABLE  + 통계성 테이블 추가 예정 +  IS ' + 통계성 테이블 추가 예정 + ' ;</v>
-      </c>
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="19"/>
     </row>
     <row r="37" spans="1:8" s="16" customFormat="1">
       <c r="A37" s="18"/>
@@ -3175,7 +3141,7 @@
     <row r="39" spans="1:8" s="16" customFormat="1">
       <c r="A39" s="18"/>
       <c r="B39" s="18"/>
-      <c r="E39" s="20"/>
+      <c r="E39" s="17"/>
       <c r="F39" s="19"/>
     </row>
     <row r="40" spans="1:8" s="16" customFormat="1">
@@ -3188,7 +3154,7 @@
       <c r="A41" s="18"/>
       <c r="B41" s="18"/>
       <c r="E41" s="17"/>
-      <c r="F41" s="19"/>
+      <c r="F41" s="18"/>
     </row>
     <row r="42" spans="1:8" s="16" customFormat="1">
       <c r="A42" s="18"/>
@@ -3700,16 +3666,10 @@
       <c r="E126" s="17"/>
       <c r="F126" s="18"/>
     </row>
-    <row r="127" spans="1:6" s="16" customFormat="1">
-      <c r="A127" s="18"/>
-      <c r="B127" s="18"/>
-      <c r="E127" s="17"/>
-      <c r="F127" s="18"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:F34" xr:uid="{9EA3090A-E262-42D4-99E5-F7D0583EC6C1}">
-    <sortState ref="A4:F34">
-      <sortCondition ref="A3:A34"/>
+  <autoFilter ref="A3:F33" xr:uid="{9EA3090A-E262-42D4-99E5-F7D0583EC6C1}">
+    <sortState ref="A4:F33">
+      <sortCondition ref="A3:A33"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="24" type="noConversion"/>
